--- a/activity/M01A05/M01A05.xlsx
+++ b/activity/M01A05/M01A05.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B31EB81-86E1-4877-B634-663BBFEFD6BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08DFB3F5-57C3-44EE-9000-206E08876A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="50">
   <si>
     <t>Observaciones</t>
   </si>
@@ -137,9 +137,6 @@
     <t>Modelo HEC-RAS 1D. Red con eje valle proyecto</t>
   </si>
   <si>
-    <t>Archivos comprimidos en formato .zip con los modelo topológicos geográficos de HEC-GeoRAS / RAS Mapper y otros de los modelos HEC-RAS.</t>
-  </si>
-  <si>
     <t>Grupo 6</t>
   </si>
   <si>
@@ -186,6 +183,12 @@
   </si>
   <si>
     <t>Modelo RAS Mapper. Red con eje valle proyecto (incluir en reporte:  planta de cada capa, líneas con direcciones vectoriales y tabla de atributos)</t>
+  </si>
+  <si>
+    <t>Cargar en la carpeta /file/hec del repositorio de datos, los archivos comprimidos del modelo RAS como HECRAS_Natural_v0.zip y HECRAS_Anthropic_v0.zip.</t>
+  </si>
+  <si>
+    <t>Banks (en el modelo de muestreo que incluye el valle suavizado, las líneas de banca paralelas solo al eje de los tramos de nuevo valle, deben ser localizadas a 150m a cada lado, esto permitirá evaluar los cortes y rellenos a analizar en entregas posteriores.)</t>
   </si>
 </sst>
 </file>
@@ -2092,12 +2095,12 @@
     <row r="1" spans="2:6" x14ac:dyDescent="0.45">
       <c r="E1" s="24"/>
       <c r="F1" s="33" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
@@ -2215,7 +2218,7 @@
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B10" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="34">
         <v>5</v>
@@ -2232,7 +2235,7 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B11" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" s="34">
         <v>5</v>
@@ -2249,7 +2252,7 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B12" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" s="34">
         <v>5</v>
@@ -2266,7 +2269,7 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B13" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" s="34">
         <v>5</v>
@@ -2283,7 +2286,7 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B14" s="15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C14" s="34">
         <v>5</v>
@@ -2300,7 +2303,7 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B15" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15" s="34">
         <v>5</v>
@@ -2317,7 +2320,7 @@
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B16" s="15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C16" s="34">
         <v>5</v>
@@ -2334,7 +2337,7 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B17" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C17" s="34">
         <v>5</v>
@@ -2351,7 +2354,7 @@
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B18" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C18" s="35">
         <v>5</v>
@@ -2368,7 +2371,7 @@
     </row>
     <row r="19" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B19" s="26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C19" s="26"/>
       <c r="D19" s="26"/>
@@ -2615,7 +2618,7 @@
     </row>
     <row r="4" spans="1:30" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B4" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C4" s="36">
         <v>0</v>
@@ -2841,7 +2844,7 @@
     </row>
     <row r="10" spans="1:30" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B10" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C10" s="36"/>
       <c r="D10" s="37"/>
@@ -2905,9 +2908,9 @@
       <c r="AC11" s="36"/>
       <c r="AD11" s="37"/>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:30" ht="61.5" x14ac:dyDescent="0.45">
       <c r="B12" s="13" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="C12" s="36"/>
       <c r="D12" s="37"/>
@@ -3666,7 +3669,7 @@
     </row>
     <row r="35" spans="1:30" ht="153.75" x14ac:dyDescent="0.45">
       <c r="B35" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C35" s="36"/>
       <c r="D35" s="37"/>
@@ -3699,7 +3702,7 @@
     </row>
     <row r="36" spans="1:30" ht="61.5" x14ac:dyDescent="0.45">
       <c r="B36" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C36" s="36"/>
       <c r="D36" s="37"/>
@@ -3732,7 +3735,7 @@
     </row>
     <row r="37" spans="1:30" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B37" s="13" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C37" s="36"/>
       <c r="D37" s="37"/>
